--- a/Penetracao_tecnologias_sucata.xlsx
+++ b/Penetracao_tecnologias_sucata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fce9e6a828229890/Doutorado/Tese/Iron and steel model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ead127730922d462/DOUTORADO/0.TESE/modelagem/modelo_bru/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="721" documentId="8_{4A340A62-AD03-4591-996C-9D43EE8C63E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D798FEA-BBB1-4151-A2DF-612861B3EE62}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{73AA50CC-4BE9-4F48-B601-43A293ED0747}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73AA50CC-4BE9-4F48-B601-43A293ED0747}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -383,7 +383,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -879,6 +879,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -886,7 +887,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1160,6 +1160,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1167,7 +1168,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1834,6 +1834,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1841,7 +1842,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3751,9 +3751,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3791,7 +3791,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3897,7 +3897,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4039,7 +4039,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4048,14 +4048,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146BC4D-2B08-4594-81F8-6131BC975722}">
   <dimension ref="A1:AF47"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>0.98566501672383067</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>0.98880746303425338</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>0.98566501672383067</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>0</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>0.01</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B12">
         <f>LN(1/B11-1)</f>
         <v>4.5951198501345898</v>
@@ -4694,7 +4694,7 @@
         <v>-4.5951198501345836</v>
       </c>
     </row>
-    <row r="21" spans="2:19">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>5</v>
       </c>
@@ -4702,8 +4702,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:19" ht="15" thickBot="1"/>
-    <row r="23" spans="2:19">
+    <row r="22" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="O23" s="4"/>
     </row>
-    <row r="24" spans="2:19">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>7</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>0.98547585648208091</v>
       </c>
     </row>
-    <row r="25" spans="2:19">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>8</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>0.97116266370909099</v>
       </c>
     </row>
-    <row r="26" spans="2:19">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>9</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>-1.6666666666666667</v>
       </c>
     </row>
-    <row r="27" spans="2:19">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>10</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>0.66549427366887892</v>
       </c>
     </row>
-    <row r="28" spans="2:19" ht="15" thickBot="1">
+    <row r="28" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
         <v>11</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:19" ht="15" thickBot="1">
+    <row r="30" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>12</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="2:19">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
         <v>13</v>
@@ -4825,7 +4825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="2:19">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>18</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="33" spans="2:22">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>19</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>0.44288262828606872</v>
       </c>
     </row>
-    <row r="34" spans="2:22" ht="15" thickBot="1">
+    <row r="34" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
         <v>20</v>
       </c>
@@ -4915,8 +4915,8 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
     </row>
-    <row r="35" spans="2:22" ht="15" thickBot="1"/>
-    <row r="36" spans="2:22">
+    <row r="35" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
         <v>21</v>
@@ -4968,7 +4968,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="2:22">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>28</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:22">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>29</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>4.9504481611159477E-279</v>
       </c>
     </row>
-    <row r="39" spans="2:22">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>30</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>2.6703321136943701E-307</v>
       </c>
     </row>
-    <row r="40" spans="2:22">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>31</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>-3.210832967359935E-241</v>
       </c>
     </row>
-    <row r="41" spans="2:22">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>32</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>5.8711317495552517</v>
       </c>
     </row>
-    <row r="42" spans="2:22" ht="15" thickBot="1">
+    <row r="42" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
         <v>33</v>
       </c>
@@ -5160,8 +5160,8 @@
         <v>-0.28911361845434669</v>
       </c>
     </row>
-    <row r="45" spans="2:22" ht="15" thickBot="1"/>
-    <row r="46" spans="2:22">
+    <row r="45" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>34</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="2:22" ht="15" thickBot="1">
+    <row r="47" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>1</v>
       </c>
@@ -5192,13 +5192,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5AF6384-6F2C-4800-834D-A9BB4A406990}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>37</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>0.185</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>0.12121999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>0.14249999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5425,7 +5425,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>0.13750000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>0.14249999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>4.1250000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>4.1250000000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -6166,7 +6166,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>0.14249999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -6565,17 +6565,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14304F9D-5B63-41E6-A40A-D96D347FDD54}">
   <dimension ref="A1:CD37"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.5703125" customWidth="1"/>
+    <col min="1" max="1" width="61.5546875" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="35" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="37" max="47" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="35" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="47" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" ht="15" thickBot="1">
+    <row r="1" spans="1:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="26" t="s">
         <v>78</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:82">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.3">
       <c r="A2" s="27"/>
       <c r="B2" s="7" t="s">
         <v>82</v>
@@ -6691,7 +6691,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:82">
+    <row r="3" spans="1:82" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>84</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:82">
+    <row r="4" spans="1:82" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>85</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>1.2222222222222223</v>
       </c>
     </row>
-    <row r="5" spans="1:82">
+    <row r="5" spans="1:82" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>86</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>1.142857142857143</v>
       </c>
     </row>
-    <row r="6" spans="1:82">
+    <row r="6" spans="1:82" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>87</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="7" spans="1:82" ht="15" thickBot="1">
+    <row r="7" spans="1:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>88</v>
       </c>
@@ -7387,12 +7387,12 @@
         <v>1.4999999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:82" ht="86.45">
+    <row r="9" spans="1:82" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:82">
+    <row r="12" spans="1:82" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>1970</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:82">
+    <row r="13" spans="1:82" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>64072</v>
       </c>
     </row>
-    <row r="14" spans="1:82">
+    <row r="14" spans="1:82" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -8176,10 +8176,10 @@
         <v>42287.520000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:82">
+    <row r="15" spans="1:82" x14ac:dyDescent="0.3">
       <c r="AZ15" s="16"/>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>84</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>3691.7004960000004</v>
       </c>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>85</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>3291.6076974000007</v>
       </c>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>86</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>5220.9017942399923</v>
       </c>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>87</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>2911.4957520000003</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="15" thickBot="1">
+    <row r="22" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>88</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>93</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>17059.705739639994</v>
       </c>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" s="23">
         <f>B24/B23</f>
         <v>0.96876313670665348</v>
@@ -9060,7 +9060,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B26" s="16">
         <f>AZ13*0.24*0.85</f>
         <v>6951.229527272717</v>
@@ -9186,7 +9186,7 @@
         <v>13070.687999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -9219,8 +9219,8 @@
       <c r="AE27" s="17"/>
       <c r="AF27" s="17"/>
     </row>
-    <row r="28" spans="1:32" ht="15" thickBot="1"/>
-    <row r="29" spans="1:32" ht="15" thickBot="1">
+    <row r="28" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="26" t="s">
         <v>78</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" s="27"/>
       <c r="B30" s="7" t="s">
         <v>82</v>
@@ -9264,7 +9264,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>84</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>85</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>0.95569620253164556</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>86</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>7495</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>87</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>7820</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>88</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>1.1282051282051282</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="28" t="s">
         <v>95</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15" thickBot="1">
+    <row r="37" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29"/>
       <c r="B37" s="31"/>
       <c r="C37" s="20" t="s">
